--- a/从零开始学Slots/从零开始学Slots-07-数值篇-WildSymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-07-数值篇-WildSymbols.xlsx
@@ -5976,6 +5976,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:I123" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -7085,5 +7088,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:O89" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-07-数值篇-WildSymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-07-数值篇-WildSymbols.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="161">
   <si>
     <r>
       <rPr>
@@ -5119,7 +5119,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5246,6 +5246,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6037,8 +6041,8 @@
       <c r="B5" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>84</v>
+      <c r="C5" s="32">
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6890,8 +6894,8 @@
       <c r="B54" s="26" t="n">
         <v>0.285714285714286</v>
       </c>
-      <c r="C54" s="15" t="s">
-        <v>138</v>
+      <c r="C54" s="32">
+        <v>2</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6901,8 +6905,8 @@
       <c r="B55" s="26" t="n">
         <v>0.142857142857143</v>
       </c>
-      <c r="C55" s="15" t="s">
-        <v>140</v>
+      <c r="C55" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6934,8 +6938,8 @@
       <c r="E57" s="16"/>
     </row>
     <row r="58" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
-        <v>145</v>
+      <c r="A58" s="32">
+        <v>3</v>
       </c>
       <c r="B58" s="25" t="n">
         <f aca="false">B56^3*B57</f>
@@ -6948,8 +6952,8 @@
       <c r="E58" s="16"/>
     </row>
     <row r="59" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15" t="s">
-        <v>147</v>
+      <c r="A59" s="32">
+        <v>4</v>
       </c>
       <c r="B59" s="25" t="n">
         <f aca="false">B56^4*B57</f>
@@ -6962,8 +6966,8 @@
       <c r="E59" s="16"/>
     </row>
     <row r="60" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="s">
-        <v>149</v>
+      <c r="A60" s="32">
+        <v>5</v>
       </c>
       <c r="B60" s="25" t="n">
         <f aca="false">B56^5</f>

--- a/从零开始学Slots/从零开始学Slots-07-数值篇-WildSymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-07-数值篇-WildSymbols.xlsx
@@ -4930,12 +4930,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -5119,7 +5120,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5249,6 +5250,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6535,7 +6548,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="E33" s="33" t="n">
         <f aca="false">C33/D33</f>
         <v>0.0449812578092461</v>
       </c>
@@ -6562,7 +6575,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E34" s="21" t="n">
+      <c r="E34" s="33" t="n">
         <f aca="false">C34/D34</f>
         <v>0.0192776819182484</v>
       </c>
@@ -6589,7 +6602,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E35" s="21" t="n">
+      <c r="E35" s="33" t="n">
         <f aca="false">C35/D35</f>
         <v>0.0144582614386863</v>
       </c>
@@ -6616,7 +6629,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="E36" s="33" t="n">
         <f aca="false">C36/D36</f>
         <v>0.0449812578092461</v>
       </c>
@@ -6643,7 +6656,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="33" t="n">
         <f aca="false">C37/D37</f>
         <v>0.0192776819182484</v>
       </c>
@@ -6670,7 +6683,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="33" t="n">
         <f aca="false">C38/D38</f>
         <v>0.0144582614386863</v>
       </c>
@@ -6697,7 +6710,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="E39" s="33" t="n">
         <f aca="false">C39/D39</f>
         <v>0.0449812578092461</v>
       </c>
@@ -6724,7 +6737,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="33" t="n">
         <f aca="false">C40/D40</f>
         <v>0.0192776819182484</v>
       </c>
@@ -6751,7 +6764,7 @@
         <f aca="false">$B$10</f>
         <v>16807</v>
       </c>
-      <c r="E41" s="21" t="n">
+      <c r="E41" s="33" t="n">
         <f aca="false">C41/D41</f>
         <v>0.0144582614386863</v>
       </c>
@@ -6823,7 +6836,7 @@
       <c r="A48" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B48" s="25" t="n">
+      <c r="B48" s="34" t="n">
         <f aca="false">G42</f>
         <v>6.09656690664604</v>
       </c>
@@ -6913,7 +6926,7 @@
       <c r="A56" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="25" t="n">
+      <c r="B56" s="34" t="n">
         <f aca="false">B54+B55</f>
         <v>0.428571428571429</v>
       </c>
@@ -6927,7 +6940,7 @@
       <c r="A57" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B57" s="25" t="n">
+      <c r="B57" s="34" t="n">
         <f aca="false">1-B56</f>
         <v>0.571428571428572</v>
       </c>
@@ -6941,7 +6954,7 @@
       <c r="A58" s="32">
         <v>3</v>
       </c>
-      <c r="B58" s="25" t="n">
+      <c r="B58" s="34" t="n">
         <f aca="false">B56^3*B57</f>
         <v>0.0449812578092461</v>
       </c>
@@ -6955,7 +6968,7 @@
       <c r="A59" s="32">
         <v>4</v>
       </c>
-      <c r="B59" s="25" t="n">
+      <c r="B59" s="34" t="n">
         <f aca="false">B56^4*B57</f>
         <v>0.0192776819182483</v>
       </c>
@@ -6969,7 +6982,7 @@
       <c r="A60" s="32">
         <v>5</v>
       </c>
-      <c r="B60" s="25" t="n">
+      <c r="B60" s="34" t="n">
         <f aca="false">B56^5</f>
         <v>0.0144582614386862</v>
       </c>
